--- a/docs/SCENARIO_EDGE_ONTOLOGY_MAPPING_20260803.xlsx
+++ b/docs/SCENARIO_EDGE_ONTOLOGY_MAPPING_20260803.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오엣지_V4.2대조" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시나리오엣지_V4.3대조" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>신규 필요</t>
+          <t>V4.3 반영</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>uses_id는 psn-id만</t>
+          <t>linked_id</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>직접 엣지 신규 (계좌↔인증서 ID)</t>
+          <t>✅ V4.3 반영 완료 — linked_id</t>
         </is>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>🟢 즉시</t>
+          <t>✅ V4.3</t>
         </is>
       </c>
     </row>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>신규 필요</t>
+          <t>V4.3 반영</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>sameAs는 psn-psn만</t>
+          <t>sameAs 확장</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>sameAs를 vt_id로 확장</t>
+          <t>✅ V4.3 반영 완료 — sameAs 확장</t>
         </is>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>🟢 즉시</t>
+          <t>✅ V4.3</t>
         </is>
       </c>
     </row>
@@ -1462,12 +1462,12 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>신규 필요</t>
+          <t>V4.3 반영</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mentions_id</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>직접 엣지 신규 (계정→게시물 기재)</t>
+          <t>✅ V4.3 반영 완료 — mentions_id</t>
         </is>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>🟢 즉시</t>
+          <t>✅ V4.3</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>신규 필요</t>
+          <t>V4.3 반영</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>accomplice_of/sameAs만 존재</t>
+          <t>knows</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>직접 엣지 신규 knows (사회관계)</t>
+          <t>✅ V4.3 반영 완료 — knows</t>
         </is>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>🟢 즉시</t>
+          <t>✅ V4.3</t>
         </is>
       </c>
     </row>
@@ -1852,12 +1852,12 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>신규 필요</t>
+          <t>V4.3 반영</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>linked_id</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>직접 엣지 신규 (전화↔계정)</t>
+          <t>✅ V4.3 반영 완료 — linked_id</t>
         </is>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>🟢 즉시</t>
+          <t>✅ V4.3</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
     <row r="1">
       <c r="A1" s="8" t="inlineStr">
         <is>
-          <t>CCOP 온톨로지 V4.2 — 시나리오 엣지 적용 검토 요약</t>
+          <t>CCOP 온톨로지 V4.3 — 시나리오 엣지 적용 검토 요약</t>
         </is>
       </c>
       <c r="B1" s="8" t="inlineStr"/>
@@ -2129,14 +2129,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CCOP V4.2 (25노드 / 60엣지)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-    </row>
+          <t>CCOP V4.3 (25노드 / 63엣지)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
@@ -2162,7 +2159,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>🟢 즉시 추가 (직접 엣지, 저위험)</t>
+          <t>✅ V4.3 반영 완료 (직접 엣지 3종 + sameAs 확장)</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -2199,10 +2196,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
@@ -2216,7 +2210,6 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>속성적 연결(식별자/사회관계/유사성)은 직접 엣지 — 무분별 추가 시 스키마 팽창으로 Text2Cypher 역행</t>
